--- a/tests/fixtures/extract_corpus_v2/dev/bundle_vv40_fea_010/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_vv40_fea_010/extracted.xlsx
@@ -490,6 +490,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -565,6 +570,21 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="A7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="B7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="D7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -771,41 +791,6 @@
       </text>
     </comment>
     <comment ref="I7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="A8" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="B8" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="D8" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="E8" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="F8" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="H8" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="I8" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1453,12 +1438,12 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>Pre-test design screening and worst-case design selection for a Ti-6Al-4V pedicle screw–rod construct under ASTM F1717 vertebrectomy surrogate loading</t>
+          <t>Pre-test design screening and worst-case selection for thoracolumbar pedicle screw–rod construct under ASTM F1717 vertebrectomy surrogate loading</t>
         </is>
       </c>
       <c r="C3" s="39" t="inlineStr">
         <is>
-          <t>A finite element model implemented in Abaqus/2023.HF3 is used to evaluate static stiffness, peak von Mises stress, and displacement of a thoracolumbar pedicle screw–rod construct in the ASTM F1717 vertebrectomy surrogate configuration. The model supports engineering down-selection of rod design variants, set-screw torque guidance, and test matrix reduction prior to design freeze. It does not replace mandatory regulatory bench testing.</t>
+          <t>The finite element model predicts static stiffness, peak von Mises stress, and displacement of a Ø5.5 mm Ti-6Al-4V ELI rod pedicle screw–rod system in the ASTM F1717 vertebrectomy surrogate configuration. The model supports engineering down-selection of two rod design variants and set-screw torque guidance prior to design freeze, and informs test matrix reduction. It does not replace mandatory regulatory bench testing.</t>
         </is>
       </c>
       <c r="D3" s="39" t="inlineStr">
@@ -1496,9 +1481,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="39" t="inlineStr">
+        <is>
+          <t>report.md</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -2094,7 +2079,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>Pre-test design screening requirement</t>
+          <t>Pre-test Design Screening Performance Requirement</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
@@ -2104,7 +2089,7 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>Model must predict static stiffness and peak stress with sufficient accuracy (within combined uncertainty) to support worst-case design selection and set-screw torque guidance, with a minimum 20% margin before physical testing; model must not be used for fretting wear or fatigue life prediction.</t>
+          <t>Model must predict static stiffness and peak stress for worst-case pedicle screw–rod geometries with sufficient accuracy to support design down-selection and verify a minimum 20% margin before physical testing; predictions must agree with ASTM F1717 bench tests within combined uncertainty bounds and quantified uncertainty intervals must encompass test-derived measurements.</t>
         </is>
       </c>
       <c r="E3" s="22" t="inlineStr">
@@ -2126,13 +2111,13 @@
       </c>
       <c r="B4" s="41" t="inlineStr">
         <is>
-          <t>Abaqus FEA model of pedicle screw–rod construct</t>
+          <t>Abaqus FEA Model of Pedicle Screw–Rod Construct (v1.7.3)</t>
         </is>
       </c>
       <c r="C4" s="24" t="n"/>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>Full 3D solid FEA model in Abaqus/Standard 2023.HF3 of a Ti-6Al-4V ELI pedicle screw–rod construct with polyaxial tulips and UHMWPE fixture blocks under ASTM F1717 vertebrectomy surrogate loading; ~4.1 million DOF; elastic–plastic material; surface-to-surface finite-sliding contact.</t>
+          <t>Full 3D solid FEA model in Abaqus/Standard 2023.HF3 of the ASTM F1717 vertebrectomy surrogate construct, including Ti-6Al-4V ELI rod/screw elastic–plastic behavior, UHMWPE blocks, surface-to-surface contact with penalty formulation, and bolt-load preload; ~4.1 million DOF.</t>
         </is>
       </c>
       <c r="E4" s="33" t="n"/>
@@ -2146,13 +2131,13 @@
       </c>
       <c r="B5" s="41" t="inlineStr">
         <is>
-          <t>ASTM F1717 bench test dataset</t>
+          <t>ASTM F1717 Static Bench Test Data (5 specimens per variant)</t>
         </is>
       </c>
       <c r="C5" s="24" t="n"/>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>Static compression-bending test data from MTS 858 frame on five specimens per variant; measurements include vertical stiffness, displacement at 400 N, load at 2% offset, and DIC surface strains on tulip exterior; fatigue run-out data used qualitatively.</t>
+          <t>Internal static compression-bending test results on MTS 858 frame per ASTM F1717; records vertical stiffness, displacement at 400 N, load to 2% offset, and DIC surface strain fields on tulip exterior for two rod diameter variants.</t>
         </is>
       </c>
       <c r="E5" s="33" t="n"/>
@@ -2166,23 +2151,35 @@
       </c>
       <c r="B6" s="41" t="inlineStr">
         <is>
-          <t>Material and input characterization dataset</t>
+          <t>Material Coupon and Input Characterization Data</t>
         </is>
       </c>
       <c r="C6" s="24" t="n"/>
       <c r="D6" s="41" t="inlineStr">
         <is>
-          <t>Tensile coupon data (n=10, ASTM E8) for Ti-6Al-4V ELI; UHMWPE compression test data; torque–tension data from 8 assemblies; CMM as-built geometry deviations on 5 parts; ring-on-disc friction measurements; XRD residual stress measurements on representative parts.</t>
+          <t>Tensile coupon data (10 coupons, ASTM E8) for Ti-6Al-4V ELI from the same heat lot; UHMWPE compression tests and supplier certificates; torque–tension data from 8 assemblies; XRD residual stress measurements; CMM as-built geometry verification on 5 parts.</t>
         </is>
       </c>
       <c r="E6" s="33" t="n"/>
       <c r="F6" s="33" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1" s="18">
-      <c r="A7" s="24" t="n"/>
-      <c r="B7" s="24" t="n"/>
+      <c r="A7" s="41" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="B7" s="41" t="inlineStr">
+        <is>
+          <t>Uncertainty Propagation and Sensitivity Analysis Results</t>
+        </is>
+      </c>
       <c r="C7" s="24" t="n"/>
-      <c r="D7" s="33" t="n"/>
+      <c r="D7" s="41" t="inlineStr">
+        <is>
+          <t>Latin Hypercube sample (n=500) on a response-surface surrogate; Sobol global sensitivity analysis (Saltelli sequence, 2,000 evaluations); predicted 95% intervals for stiffness (28.4–31.7 N/mm) and peak von Mises stress (736–828 MPa at 400 N).</t>
+        </is>
+      </c>
       <c r="E7" s="33" t="n"/>
       <c r="F7" s="33" t="n"/>
     </row>
@@ -2322,7 +2319,7 @@
     <row r="3" ht="32.8" customHeight="1" s="18">
       <c r="A3" s="39" t="inlineStr">
         <is>
-          <t>Vertical stiffness comparison (model vs. ASTM F1717 bench test)</t>
+          <t>Vertical Stiffness Comparison (Model vs. ASTM F1717 Bench Test)</t>
         </is>
       </c>
       <c r="B3" s="39" t="inlineStr">
@@ -2337,12 +2334,12 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>Model-predicted vertical stiffness compared to test mean across five specimens under ASTM F1717 static compression-bending</t>
+          <t>Model-predicted vertical stiffness (slope over 0.5–3.0 mm travel) compared to test mean from five specimens under ASTM F1717 static compression-bending protocol.</t>
         </is>
       </c>
       <c r="E3" s="39" t="inlineStr">
         <is>
-          <t>Test mean 29.6 N/mm (SD 0.7 N/mm) from MTS 858 frame with calibrated load cell and dual LVDTs</t>
+          <t>Test mean 29.6 N/mm (SD 0.7 N/mm) from five specimens</t>
         </is>
       </c>
       <c r="F3" s="39" t="inlineStr">
@@ -2352,7 +2349,7 @@
       </c>
       <c r="G3" s="39" t="inlineStr">
         <is>
-          <t>Latin Hypercube sampling (n=500) on response surface; 95% predicted interval 28.4–31.7 N/mm; combined test+model uncertainty 3.0%</t>
+          <t>Combined measurement and model uncertainty estimated at 3.0%; Latin Hypercube propagation yields 95% interval 28.4–31.7 N/mm</t>
         </is>
       </c>
       <c r="H3" s="39" t="inlineStr">
@@ -2369,7 +2366,7 @@
     <row r="4" ht="15" customHeight="1" s="18">
       <c r="A4" s="41" t="inlineStr">
         <is>
-          <t>Displacement at 400 N comparison (model vs. bench test)</t>
+          <t>Displacement at 400 N Comparison</t>
         </is>
       </c>
       <c r="B4" s="41" t="inlineStr">
@@ -2380,12 +2377,12 @@
       <c r="C4" s="33" t="n"/>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>Model-predicted displacement at 400 N load compared to bench test; correction applied for measured UHMWPE batch modulus (0.92 GPa vs. assumed 0.95 GPa)</t>
+          <t>Model-predicted vertical displacement at 400 N load compared to test measurement; corrected for measured batch UHMWPE modulus (0.92 GPa vs. assumed 0.95 GPa).</t>
         </is>
       </c>
       <c r="E4" s="41" t="inlineStr">
         <is>
-          <t>Test measurement 13.5 mm (LVDT ±0.02 mm)</t>
+          <t>Test measurement 13.5 mm</t>
         </is>
       </c>
       <c r="F4" s="41" t="inlineStr">
@@ -2395,12 +2392,12 @@
       </c>
       <c r="G4" s="41" t="inlineStr">
         <is>
-          <t>Input uncertainty propagation; UHMWPE modulus batch correction applied</t>
+          <t>Input uncertainty correction applied; residual difference assessed against predicted uncertainty range</t>
         </is>
       </c>
       <c r="H4" s="41" t="inlineStr">
         <is>
-          <t>Corrected model 12.8 mm vs. test 13.5 mm; residual difference 5.2%; consistent with predicted uncertainty range</t>
+          <t>Corrected model 12.8 mm vs. test 13.5 mm; residual difference 5.2%; uncorrected model 12.3 mm (9.1% difference before UHMWPE correction)</t>
         </is>
       </c>
       <c r="I4" s="42" t="inlineStr">
@@ -2412,7 +2409,7 @@
     <row r="5" ht="15" customHeight="1" s="18">
       <c r="A5" s="41" t="inlineStr">
         <is>
-          <t>Peak strain field comparison (DIC vs. model surface strains at tulip crown)</t>
+          <t>Load to 2% Offset in Construct Bending</t>
         </is>
       </c>
       <c r="B5" s="41" t="inlineStr">
@@ -2423,12 +2420,12 @@
       <c r="C5" s="33" t="n"/>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>Qualitative hotspot location and quantitative peak surface strains at tulip crown compared between DIC measurements and model predictions</t>
+          <t>Model-predicted load at 2% bending offset compared to test mean from five specimens; assesses onset of yielding prediction.</t>
         </is>
       </c>
       <c r="E5" s="41" t="inlineStr">
         <is>
-          <t>DIC surface strain measurements; DIC uncertainty ~75 με; speckle-dependent uncertainty 4–6%</t>
+          <t>Test mean 980 N (SD 22 N)</t>
         </is>
       </c>
       <c r="F5" s="41" t="inlineStr">
@@ -2438,24 +2435,24 @@
       </c>
       <c r="G5" s="41" t="inlineStr">
         <is>
-          <t>DIC measurement uncertainty bounds (4–6% depending on speckle quality)</t>
+          <t>Combined test and model uncertainty estimated at 5.1%</t>
         </is>
       </c>
       <c r="H5" s="41" t="inlineStr">
         <is>
-          <t>Peak strain difference 8.4% on average; DIC uncertainty bounds encompass 4–6%; qualitative hotspot location matches</t>
+          <t>Model 1,012 N vs. test 980 N; difference +3.3%; within combined uncertainty of 5.1%</t>
         </is>
       </c>
       <c r="I5" s="42" t="inlineStr">
         <is>
-          <t>Inconclusive</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="18">
       <c r="A6" s="41" t="inlineStr">
         <is>
-          <t>Load at 2% offset comparison (model vs. bench test)</t>
+          <t>DIC Surface Strain Field Comparison at Tulip Crown</t>
         </is>
       </c>
       <c r="B6" s="41" t="inlineStr">
@@ -2466,12 +2463,12 @@
       <c r="C6" s="33" t="n"/>
       <c r="D6" s="41" t="inlineStr">
         <is>
-          <t>Model-predicted load at 2% construct bending offset compared to test mean</t>
+          <t>Qualitative hotspot location and quantitative peak surface strain comparison between FEA predictions and DIC measurements on tulip exterior.</t>
         </is>
       </c>
       <c r="E6" s="41" t="inlineStr">
         <is>
-          <t>Test mean 980 N (SD 22 N)</t>
+          <t>DIC strain field measurements (uncertainty ~75 με; speckle-dependent 4–6% bounds)</t>
         </is>
       </c>
       <c r="F6" s="41" t="inlineStr">
@@ -2481,12 +2478,12 @@
       </c>
       <c r="G6" s="41" t="inlineStr">
         <is>
-          <t>Combined test and model uncertainty estimated at 5.1%</t>
+          <t>DIC measurement uncertainty characterization; speckle-quality-dependent bounds</t>
         </is>
       </c>
       <c r="H6" s="41" t="inlineStr">
         <is>
-          <t>Model predicted 1,012 N vs. test mean 980 N; difference +3.3%; within combined uncertainty of 5.1%</t>
+          <t>Hotspot location matches qualitatively; quantitative peak strain difference 8.4% average; within DIC uncertainty bounds of 4–6% at best, marginally outside at worst</t>
         </is>
       </c>
       <c r="I6" s="42" t="inlineStr">
@@ -2498,7 +2495,7 @@
     <row r="7" ht="15" customHeight="1" s="18">
       <c r="A7" s="41" t="inlineStr">
         <is>
-          <t>Mesh convergence study (GCI / Richardson extrapolation)</t>
+          <t>Mesh Convergence Study (Richardson Extrapolation)</t>
         </is>
       </c>
       <c r="B7" s="41" t="inlineStr">
@@ -2509,12 +2506,12 @@
       <c r="C7" s="33" t="n"/>
       <c r="D7" s="41" t="inlineStr">
         <is>
-          <t>Three nested meshes (M1/M2/M3) with Richardson extrapolation on peak von Mises stress at set-screw root and on construct vertical stiffness</t>
+          <t>Three nested meshes (M1/M2/M3) with halved element sizes at hot spots; Richardson extrapolation applied to estimate grid-induced error in peak von Mises stress and vertical stiffness.</t>
         </is>
       </c>
       <c r="E7" s="41" t="inlineStr">
         <is>
-          <t>Asymptotic Richardson-extrapolated value; observed convergence order p ≈ 1.85</t>
+          <t>Richardson-extrapolated asymptotic solution</t>
         </is>
       </c>
       <c r="F7" s="41" t="inlineStr">
@@ -2524,12 +2521,12 @@
       </c>
       <c r="G7" s="41" t="inlineStr">
         <is>
-          <t>Richardson extrapolation; Grid Convergence Index estimated</t>
+          <t>Richardson extrapolation with observed convergence order p≈1.85; GCI-equivalent error estimate</t>
         </is>
       </c>
       <c r="H7" s="41" t="inlineStr">
         <is>
-          <t>Grid error at production mesh (0.20 mm local): 3.2% for peak von Mises; stiffness change M2 to M3 &lt; 0.7%</t>
+          <t>Grid error at production mesh (0.20 mm): 3.2% in peak stress; stiffness change M2 to M3 &lt;0.7%; Hertzian contact benchmark within 4.5%, NAFEMS LE10 within 1.2%</t>
         </is>
       </c>
       <c r="I7" s="42" t="inlineStr">
@@ -2539,43 +2536,14 @@
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="18">
-      <c r="A8" s="41" t="inlineStr">
-        <is>
-          <t>Code verification benchmarks (NAFEMS and analytical solutions)</t>
-        </is>
-      </c>
-      <c r="B8" s="41" t="inlineStr">
-        <is>
-          <t>ValidationResult</t>
-        </is>
-      </c>
+      <c r="A8" s="24" t="n"/>
+      <c r="B8" s="24" t="n"/>
       <c r="C8" s="33" t="n"/>
-      <c r="D8" s="41" t="inlineStr">
-        <is>
-          <t>Three benchmark problems run to verify element and solver behavior: thick cylinder under pressure (Lamé), Hertzian contact, and NAFEMS LE10 plate bending</t>
-        </is>
-      </c>
-      <c r="E8" s="41" t="inlineStr">
-        <is>
-          <t>Analytical solutions (Lamé, Hertz) and NAFEMS benchmark reference values</t>
-        </is>
-      </c>
-      <c r="F8" s="41" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="D8" s="33" t="n"/>
+      <c r="E8" s="25" t="n"/>
+      <c r="F8" s="33" t="n"/>
       <c r="G8" s="33" t="n"/>
-      <c r="H8" s="41" t="inlineStr">
-        <is>
-          <t>Hoop stress error 0.8%; peak contact pressure within 4.5%; NAFEMS LE10 deflection difference 1.2%; patch test constant stress error &lt; 0.3%</t>
-        </is>
-      </c>
-      <c r="I8" s="42" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
+      <c r="H8" s="33" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1" s="18">
       <c r="A9" s="24" t="n"/>
@@ -2782,12 +2750,12 @@
       </c>
       <c r="E5" s="42" t="inlineStr">
         <is>
-          <t>Commercial solver with documented QA, version-controlled environment, and regression/CI testing</t>
+          <t>Commercial solver with documented quality controls; version-controlled scripts; internal regression testing</t>
         </is>
       </c>
       <c r="F5" s="41" t="inlineStr">
         <is>
-          <t>Abaqus/Standard 2023.HF3 is a widely certified commercial solver. The scripting environment (Python 3.10, numpy 1.26) is reproducible via a conda lockfile. Model package versioned in GitLab (tag v1.7.3, commit e1a8ab5). Continuous integration executes unit checks (flake8, pytest, 82% coverage) and a smoke simulation on every commit. Deterministic reproducibility confirmed: max numerical jitter &lt; 0.1% in peak stress. An independent analyst reproduced the primary validation case on different hardware with results within 0.7% (stress) and 0.4% (stiffness).</t>
+          <t>Abaqus/Standard 2023.HF3 is a commercially certified solver used on documented hardware (RHEL 8.8). Pre/post scripts are version-controlled in GitLab (tag v1.7.3, commit e1a8ab5) with a conda lockfile ensuring environment reproducibility. Continuous integration runs flake8, pytest (82% coverage), and a smoke simulation on every commit. Peer review checklist completed by an independent analyst. Independent reproduction on different hardware (Windows 11) confirmed peak stress within 0.7% and stiffness within 0.4%. All outputs archived in Agile PLM with immutable audit trails.</t>
         </is>
       </c>
       <c r="G5" s="41" t="inlineStr">
@@ -2815,12 +2783,12 @@
       </c>
       <c r="E6" s="42" t="inlineStr">
         <is>
-          <t>Comparison to analytical or established benchmark solutions demonstrating correct implementation of governing equations</t>
+          <t>Benchmarks against analytical solutions demonstrating solver correctness for relevant physics</t>
         </is>
       </c>
       <c r="F6" s="41" t="inlineStr">
         <is>
-          <t>Three benchmark problems executed: (1) thick cylinder under pressure — hoop stress within 0.8% of Lamé analytical solution at 0.25 mm mesh; (2) Hertzian contact — peak pressure within 4.5% of theory after mesh densification; (3) NAFEMS LE10 plate bending — deflection within 1.2% of reference. Element patch test reproduces constant stress state to &lt; 0.3%. Contact penalty scaling validated against known two-block compliance within 3.8%.</t>
+          <t>Three benchmark problems executed: (1) Lamé thick-cylinder hoop stress within 0.8% of analytical at 0.25 mm mesh; (2) Hertzian sphere–flat contact peak pressure within 4.5% of theory after local mesh densification; (3) NAFEMS LE10 plate bending deflection within 1.2%. Patch test for linear elasticity reproduces constant stress state with error &lt;0.3%. Contact formulation validated against two-block compression with known compliance, reproducing measured stiffness within 3.8%.</t>
         </is>
       </c>
       <c r="G6" s="41" t="inlineStr">
@@ -2848,12 +2816,12 @@
       </c>
       <c r="E7" s="42" t="inlineStr">
         <is>
-          <t>Mesh convergence demonstrated with quantified grid uncertainty for critical response quantities</t>
+          <t>Mesh convergence demonstrated with quantified GCI or Richardson extrapolation estimate below acceptable threshold</t>
         </is>
       </c>
       <c r="F7" s="41" t="inlineStr">
         <is>
-          <t>Three nested meshes (M1: ~1.9M DOF, M2: ~3.1M DOF, M3: ~6.0M DOF) created by halving element sizes at hot spots. Richardson extrapolation with observed order p ≈ 1.85 applied to peak von Mises at set-screw root; GCI-equivalent grid error at production mesh is 3.2%. Construct stiffness changes &lt; 0.7% from M2 to M3. Temporal increment halving causes &lt; 0.2% change in peak stress, confirming negligible time-step error. Contact penalty sensitivity study (×0.5, ×2) shows ±~1.5% peak stress variation.</t>
+          <t>Three nested meshes (M1: ~1.9M DOF, M2: ~3.1M DOF, M3: ~6.0M DOF) with halved element sizes at thread root hot spots. Richardson extrapolation with observed order p≈1.85 gives estimated grid error of 3.2% at production mesh (0.20 mm local) for peak von Mises. Vertical stiffness changes &lt;0.7% from M2 to M3. Temporal increment halving changes peak stress &lt;0.2%. Mesh quality metrics documented (max aspect ratio &lt;4, Jacobian &gt;0.6). Contact normal penalty sensitivity study (×0.5, ×2) shows peak stress sensitivity of −1.9%/+1.1%.</t>
         </is>
       </c>
       <c r="G7" s="41" t="inlineStr">
@@ -2881,12 +2849,12 @@
       </c>
       <c r="E8" s="42" t="inlineStr">
         <is>
-          <t>Iterative solver convergence demonstrated with documented residual targets and convergence monitoring</t>
+          <t>Documented convergence tolerances and confirmation that iterative solver residuals meet targets</t>
         </is>
       </c>
       <c r="F8" s="41" t="inlineStr">
         <is>
-          <t>Full Newton solver with tight tolerances: residual norm &lt; 1e-6, displacement increment &lt; 1e-5 mm. Automatic incrementation with max increment 0.1 mm; increment halving study shows &lt; 0.2% change in peak stress. Contact stabilization tuned via penalty scaling study; penetrations limited to &lt; 0.5 μm. Nonlinear geometry enabled; automatic stabilization off. Kinetic/internal energy ratio &lt; 0.5% confirms quasi-static assumption.</t>
+          <t>Full Newton nonlinear solver with residual norm convergence tolerance &lt;1e-6 and displacement increment &lt;1e-5 mm. Nonlinear geometry enabled; automatic stabilization disabled. Contact stabilization penalty scaling validated via dedicated study with penetrations limited to &lt;0.5 μm. Automatic time incrementation with max increment 0.1 mm; quasi-static inertia check confirms KE/IE &lt;0.5%. Deterministic reproducibility confirmed with numerical jitter in peak stress &lt;0.1% across repeated runs.</t>
         </is>
       </c>
       <c r="G8" s="41" t="inlineStr">
@@ -2914,12 +2882,12 @@
       </c>
       <c r="E9" s="42" t="inlineStr">
         <is>
-          <t>Independent peer review of model setup, boundary conditions, and post-processing; documented review process</t>
+          <t>Independent review of model setup; boundary conditions verified against test configuration; mesh quality confirmed</t>
         </is>
       </c>
       <c r="F9" s="41" t="inlineStr">
         <is>
-          <t>Peer review checklist completed by a modeling specialist not involved in geometry preparation; comments and dispositions captured in a review log. Each validation comparison linked to a unique YAML run configuration with hashes of input meshes and material cards, cross-referenced to test IDs. Independent analyst reproduced the primary validation case on different hardware (Windows 11, Abaqus/2023) confirming results within 0.7%/0.4%. All raw data archived in Agile PLM with immutable audit trails. Boundary conditions, fixture dimensions, and gage length verified against ASTM F1717 and measured values.</t>
+          <t>Peer review checklist completed by a modeling specialist not involved in geometry preparation; comments and dispositions recorded in review log. Boundary conditions verified against ASTM F1717 fixture dimensions (block gage length 76 ±0.2 mm, hole positions ±0.1 mm). All input files and meshes versioned in GitLab; YAML configuration files with hashes cross-referenced to test IDs. Independent reproduction by a second analyst on different hardware confirmed results. Mesh quality metrics (aspect ratio, Jacobian) documented in Appendix C.</t>
         </is>
       </c>
       <c r="G9" s="41" t="inlineStr">
@@ -2947,12 +2915,12 @@
       </c>
       <c r="E10" s="42" t="inlineStr">
         <is>
-          <t>Governing equations and constitutive model choices justified; known limitations documented</t>
+          <t>Governing equations justified for physics at hand; key assumptions documented with supporting rationale; known limitations stated</t>
         </is>
       </c>
       <c r="F10" s="41" t="inlineStr">
         <is>
-          <t>Elastic–plastic isotropic hardening (Voce law, R²=0.998) for Ti-6Al-4V ELI is justified by coupon testing. Linear elastic UHMWPE justified by rate-sweep data (Appendix B) confirming rate-insensitive behavior at test conditions. Quasi-static assumption validated by KE/IE &lt; 0.5%. Residual stresses neglected based on XRD measurements showing &lt; 30 MPa mean, small relative to operating stresses. Constant Coulomb friction acknowledged as simplification; sensitivity checked. Micro-roughness, fretting/wear, and cyclic hysteresis are explicitly excluded from scope and documented as limitations. Symmetry not assumed due to asymmetric load path — full construct modeled.</t>
+          <t>Elastic–plastic constitutive model with Voce isotropic hardening is justified for Ti-6Al-4V ELI under quasi-static loading; Voce fit R²=0.998. UHMWPE modeled as linear elastic with rate-insensitivity validated by rate-sweep data (Appendix B). Quasi-static assumption validated via KE/IE &lt;0.5%. Residual stresses neglected based on XRD measurements (&lt;30 MPa mean, small relative to operating stresses). Coulomb friction with constant coefficients is a simplification; velocity dependence not modeled. Micro-roughness and fretting at set-screw–rod interface not resolved; explicitly flagged as out-of-scope limitation. Symmetry not applied due to asymmetric load path.</t>
         </is>
       </c>
       <c r="G10" s="41" t="inlineStr">
@@ -2980,12 +2948,12 @@
       </c>
       <c r="E11" s="42" t="inlineStr">
         <is>
-          <t>Input data measured or characterized with uncertainty; influential inputs identified through sensitivity analysis</t>
+          <t>Material properties from measured specimens; geometry from CMM; boundary conditions from measurements; input uncertainties characterized</t>
         </is>
       </c>
       <c r="F11" s="41" t="inlineStr">
         <is>
-          <t>Geometry from SolidWorks 2024 CAD with CMM as-built verification on 5 parts (max deviation ±0.03 mm). Material properties from 10 tensile coupons (ASTM E8) from the same heat lot as test constructs; plasticity fit R²=0.998. Preload from torque–tension testing on 8 assemblies with calibrated torque wrench and ultrasonic bolt elongation (R²=0.93); scatter modeled as normal SD 0.8 kN. Friction from literature plus two ring-on-disc measurements; assigned uniform uncertainty ranges. UHMWPE modulus from supplier certification and in-house compression tests; batch-specific values used for comparison corrections. Sobol global sensitivity analysis (2,000 evaluations) identified dominant inputs: preload (index 0.43), Ti–Ti friction (0.22), rod diameter (0.18) for peak stress; UHMWPE modulus (0.36) and working length (0.31) for stiffness.</t>
+          <t>Geometry from SolidWorks CAD with CMM as-built verification on 5 parts (rod diameter deviation +0.03/−0.01 mm). Ti-6Al-4V ELI elastic–plastic properties from 10 tensile coupons (ASTM E8) from the same heat lot as test constructs; mean E=113±2 GPa, σ₀.₂%=860±25 MPa. UHMWPE modulus from supplier certificate and in-house compression tests; batch-specific values (0.92 GPa) used in corrected validation runs. Preload from 8 torque–tension assemblies using calibrated torque wrench and ultrasonic elongation (R²=0.93, SD 0.8 kN). Friction from literature plus two ring-on-disc measurements; assigned uniform distributions. Sobol sensitivity analysis (2,000 evaluations) ranked all influential inputs; results drove measurement priorities (e.g., batch-specific UHMWPE modulus).</t>
         </is>
       </c>
       <c r="G11" s="41" t="inlineStr">
@@ -3013,12 +2981,12 @@
       </c>
       <c r="E12" s="42" t="inlineStr">
         <is>
-          <t>Sufficient specimens tested with characterization of sample variability; production-representative samples</t>
+          <t>Adequate number of production-representative specimens; statistical characterization of variability</t>
         </is>
       </c>
       <c r="F12" s="41" t="inlineStr">
         <is>
-          <t>Five specimens per variant tested under ASTM F1717 static compression-bending; test mean and SD reported (stiffness SD 0.7 N/mm; load at 2% offset SD 22 N). Rod and screw specimens from production lots; UHMWPE blocks per ASTM F1717. Constructs assembled with calibrated torque wrench; working length and rod seating verified and recorded per specimen. Sample size of n=5 is modest but consistent with ASTM F1717 practice; batch-specific UHMWPE modulus measured to correct for within-batch variation.</t>
+          <t>Five specimens per rod variant tested per ASTM F1717; test mean and standard deviation reported (stiffness SD 0.7 N/mm; load to 2% offset SD 22 N). Constructs assembled from the same production lots as FEA input material coupons, providing production representativeness. Preload window 5.0–7.0 kN observed across assemblies and recorded. Sample size of 5 per variant is consistent with ASTM F1717 practice but is modest; no formal power analysis reported. Two rod diameter variants covered.</t>
         </is>
       </c>
       <c r="G12" s="41" t="inlineStr">
@@ -3046,12 +3014,12 @@
       </c>
       <c r="E13" s="42" t="inlineStr">
         <is>
-          <t>Calibrated instrumentation, controlled test conditions, documented measurement uncertainty</t>
+          <t>Calibrated instrumentation with characterized uncertainty; test protocol per recognized standard; controlled environment</t>
         </is>
       </c>
       <c r="F13" s="41" t="inlineStr">
         <is>
-          <t>Tests conducted on MTS 858 frame per ASTM F1717 at 6 mm/min displacement control. Load cell ±0.25% FS; LVDT ±0.02 mm; DIC strain uncertainty ~75 με (speckle-dependent 4–6%). Set-screw torque applied with calibrated wrench to 6.0 N·m; preload verified with ultrasonic bolt elongation. Fixture dimensions and gage length measured (76 ± 0.2 mm; hole positions ±0.1 mm). Construct working length and rod seating depth recorded per specimen and fed into corresponding simulation inputs. Fatigue tests conducted at R=0.1 up to 5 million cycles for qualitative trend confirmation.</t>
+          <t>Tests conducted per ASTM F1717-21 on an MTS 858 frame in displacement control at 6 mm/min. Instrumentation: 20 kN load cell (±0.25% FS), dual LVDTs (±0.02 mm), DIC for surface strain (~75 με uncertainty). Set-screw torque applied with a calibrated torque wrench to 6.0 N·m; ultrasonic verification of preload. Construct working length and rod seating depth recorded and fed into simulation inputs. Gage length 76 ±0.2 mm. DIC uncertainty characterized as speckle-quality dependent (4–6%). Environmental conditions (temperature, moisture) assumed nominal laboratory; noted as minor limitation for UHMWPE.</t>
         </is>
       </c>
       <c r="G13" s="41" t="inlineStr">
@@ -3079,12 +3047,12 @@
       </c>
       <c r="E14" s="42" t="inlineStr">
         <is>
-          <t>Demonstrated alignment between model inputs and experimental test conditions; measurement uncertainty propagated into comparison</t>
+          <t>Model input parameters demonstrably match experimental test conditions; boundary condition correspondence verified; measurement uncertainties propagated</t>
         </is>
       </c>
       <c r="F14" s="41" t="inlineStr">
         <is>
-          <t>Fixture and gage length matched between model and test (76 ± 0.2 mm); hole positions within ±0.1 mm. Set-screw preload in model calibrated via ultrasonic elongation measurement from the same torque level (6.0 N·m) used in tests. Working length and rod seating depth recorded per specimen and used as model inputs for specific comparison runs. UHMWPE batch modulus (0.92 GPa measured vs. 0.95 GPa nominal) applied as correction to displacement prediction. Preload scatter modeled as normal distribution matching measured SD. Sensitivity analysis confirmed which input deviations dominate residual comparison discrepancies.</t>
+          <t>Fixture geometry and boundary conditions replicated in the model; gage length within tolerance (76 ±0.2 mm). Set-screw preload matched via torque–tension calibration and ultrasonic verification (nominal 6.5 kN; test window 5.0–7.0 kN encompassed by simulated range). Batch-specific UHMWPE modulus (0.92 GPa) substituted in corrected validation run, reducing displacement residual from 9.1% to 5.2%. Working length and rod seating depth measured per specimen and fed into corresponding simulation runs. Each validation comparison linked to a unique YAML configuration file with input hashes. Measurement uncertainties (load cell, LVDT, DIC) characterized and used in combined uncertainty estimation.</t>
         </is>
       </c>
       <c r="G14" s="41" t="inlineStr">
@@ -3112,12 +3080,12 @@
       </c>
       <c r="E15" s="42" t="inlineStr">
         <is>
-          <t>Quantitative metrics comparing model predictions to experimental data across multiple quantities; uncertainty bands reported</t>
+          <t>Quantitative agreement metrics reported for multiple QoIs; comparison within combined uncertainty bounds; uncertainty bands reported</t>
         </is>
       </c>
       <c r="F15" s="41" t="inlineStr">
         <is>
-          <t>Four quantitative comparison metrics reported: (1) vertical stiffness — model 30.0 vs. test 29.6 N/mm, +1.4%, within combined uncertainty 3.0%; (2) displacement at 400 N — corrected model 12.8 vs. test 13.5 mm, 5.2% residual; (3) peak strains at tulip crown — 8.4% average difference, partially explained by DIC uncertainty (4–6%); (4) load at 2% offset — model 1,012 vs. test 980 N, +3.3%, within combined uncertainty 5.1%. LHS uncertainty propagation yields 95% interval 28.4–31.7 N/mm encompassing test mean. Qualitative DIC hotspot location agreement confirmed. Model-to-test residual bias shown to be small relative to propagated uncertainty spread.</t>
+          <t>Four quantitative comparisons reported: (1) vertical stiffness: +1.4% difference, within combined uncertainty of 3.0%; (2) displacement at 400 N: 5.2% residual after UHMWPE correction, within predicted uncertainty range; (3) load to 2% offset: +3.3%, within combined uncertainty of 5.1%; (4) DIC peak strain at tulip crown: 8.4% average difference, partially within DIC uncertainty bounds. Propagated 95% stiffness interval (28.4–31.7 N/mm) encompasses test mean 29.6 N/mm. Peak von Mises 95% interval 736–828 MPa reported. Multiple comparison points (stiffness, displacement, load onset, strain field) assessed. Residual bias characterized as small relative to uncertainty spreads.</t>
         </is>
       </c>
       <c r="G15" s="41" t="inlineStr">
@@ -3145,12 +3113,12 @@
       </c>
       <c r="E16" s="42" t="inlineStr">
         <is>
-          <t>QoIs directly address the engineering decision; measurable both computationally and experimentally</t>
+          <t>QoIs directly address the engineering decision (worst-case stress and stiffness margin); measurable both computationally and experimentally</t>
         </is>
       </c>
       <c r="F16" s="41" t="inlineStr">
         <is>
-          <t>Primary QoIs — vertical stiffness, peak von Mises stress, and displacement at 400 N — directly support the stated decisions: worst-case design down-selection (stress margin &gt; 20%) and set-screw torque guidance (microslip check). All QoIs are measurable both in FEA and in the ASTM F1717 bench test. Sensitivity analysis confirms which inputs govern each QoI, strengthening the relevance argument. The fraction of runs exceeding 0.2% offset at 400 N (0%) directly addresses the elastic regime requirement. Limitations on inapplicable QoIs (fretting wear, fatigue life) are explicitly documented.</t>
+          <t>Primary QoIs are vertical construct stiffness and peak von Mises stress at the set-screw root — directly linked to the engineering questions of structural margin and microslip avoidance. Stiffness is measurable with load cell and LVDT in tests and extracted directly from FEA force–displacement output. Peak stress is extracted from FEA at the identified critical location; surface strain approximation provided by DIC for partial experimental corroboration. Secondary QoI (displacement at 400 N, load to 2% offset) provide additional coverage of load-path fidelity. All QoIs are decision-relevant for pre-test design screening.</t>
         </is>
       </c>
       <c r="G16" s="41" t="inlineStr">
@@ -3178,12 +3146,12 @@
       </c>
       <c r="E17" s="42" t="inlineStr">
         <is>
-          <t>Validation conditions (geometry, loading, material, operating regime) match the intended use; gaps identified and assessed</t>
+          <t>Validation conditions match COU in geometry, loading, and operating regime; gaps to full COU envelope identified and assessed</t>
         </is>
       </c>
       <c r="F17" s="41" t="inlineStr">
         <is>
-          <t>Validation tests use the same ASTM F1717 vertebrectomy surrogate configuration, same rod diameter (5.5 mm worst case), same gage length (76 mm), same loading mode (static compression-bending to 6 mm), and same material lot as the COU. Preload and friction conditions match. Coverage includes the two relevant rod diameters and the design preload window. Identified gaps: (1) only vertebrectomy configuration covered — other standard configurations (e.g., F1798) not validated; (2) cyclic/fatigue loading not within predictive scope; (3) environmental conditions (temperature, moisture effects on UHMWPE) assumed nominal; (4) micro-scale fretting at set-screw–rod interface not modeled. All gaps are documented and judged not decision-critical for the stated pre-test screening COU.</t>
+          <t>Validation tests performed under the same ASTM F1717 vertebrectomy surrogate configuration, same rod geometry (5.5 mm and 6.0 mm diameters), same quasi-static loading rate, same fixture and gage length as the COU. Preload range in tests encompasses the simulated range. Key gap: fretting and microslip under cyclic loading not validated (explicitly flagged as out-of-scope); fatigue comparisons are qualitative only. COU is limited to static pre-test screening; cyclic life prediction explicitly excluded. No coverage of other ASTM standards (e.g., F1798). Environmental deviations from nominal laboratory conditions not validated. Gaps are documented and judged non-decision-critical for the stated COU.</t>
         </is>
       </c>
       <c r="G17" s="41" t="inlineStr">
@@ -3272,7 +3240,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>The FEA model demonstrates adequate credibility for its stated COU of pre-test design screening and worst-case design selection under ASTM F1717 vertebrectomy surrogate loading. Verification evidence (benchmarks, mesh convergence with 3.2% GCI, tight solver tolerances) establishes numerical soundness. Validation against five-specimen static bench tests shows agreement within combined uncertainty across four quantitative metrics (stiffness +1.4%, displacement 5.2% post-correction, load at 2% offset +3.3%). Inputs are largely measured from production lots with full uncertainty characterization; Sobol sensitivity analysis identifies and controls dominant uncertainty sources. LHS uncertainty propagation yields a 95% predicted stiffness interval encompassing the test-derived mean. Process controls (version control, CI, peer review, independent reproduction, PLM archiving) reduce use-error risk. Residual gaps (microslip, fretting, fatigue life, environmental effects, non-vertebrectomy configurations) are explicitly documented as out of scope and are not decision-critical for pre-test screening. Acceptance is conditional on: (1) maintaining documented software version and solver settings or re-running verification checks upon upgrade; (2) using batch-specific measured inputs (UHMWPE modulus, set-screw preload) where possible; (3) restricting interpretations to static stiffness and stress screening — no direct inference on fretting wear or fatigue life without dedicated additional model development and validation.</t>
+          <t>The pedicle screw–rod FEA model demonstrates adequate credibility for its stated purpose of pre-test design screening and worst-case selection under ASTM F1717 static loading. All primary quantitative validation comparisons (stiffness +1.4%, displacement 5.2% after input correction, load to 2% offset +3.3%) fall within combined test and model uncertainty bounds. Mesh convergence, benchmark verification, and uncertainty propagation are thorough. Inputs are measured from production-representative specimens and well-characterized. Residual gaps (microslip/fretting under cyclic loading; applicability to other standards; environmental effects on UHMWPE) are explicitly bounded and non-decision-critical for the COU. Acceptance is conditioned on: (a) maintaining the documented software version and solver settings, or re-running verification checks upon upgrade; (b) using batch-measured UHMWPE modulus and set-screw preload as model inputs for each test batch; and (c) restricting model use to static pre-test screening — no inference on fretting wear, fatigue life, or configurations outside the vertebrectomy surrogate without additional dedicated validation.</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
